--- a/Ledoit_Wolf_Results_yearly.xlsx
+++ b/Ledoit_Wolf_Results_yearly.xlsx
@@ -505,10 +505,10 @@
         <v>16.05836</v>
       </c>
       <c r="C2" t="n">
-        <v>21.37444</v>
+        <v>21.37443</v>
       </c>
       <c r="D2" t="n">
-        <v>17.53535</v>
+        <v>17.53534</v>
       </c>
       <c r="E2" t="n">
         <v>12.5435</v>
@@ -540,10 +540,10 @@
         <v>41639</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3542</v>
+        <v>17.35419</v>
       </c>
       <c r="C3" t="n">
-        <v>30.84288</v>
+        <v>30.84289</v>
       </c>
       <c r="D3" t="n">
         <v>27.78144</v>
@@ -564,7 +564,7 @@
         <v>10.02867</v>
       </c>
       <c r="J3" t="n">
-        <v>19.30522</v>
+        <v>19.30521</v>
       </c>
       <c r="K3" t="n">
         <v>3.91087</v>
@@ -593,7 +593,7 @@
         <v>0.47997</v>
       </c>
       <c r="G4" t="n">
-        <v>77.27982</v>
+        <v>77.27983999999999</v>
       </c>
       <c r="H4" t="n">
         <v>2.67</v>
@@ -616,7 +616,7 @@
         <v>42369</v>
       </c>
       <c r="B5" t="n">
-        <v>23.66844</v>
+        <v>23.66843</v>
       </c>
       <c r="C5" t="n">
         <v>48.27262</v>
@@ -631,7 +631,7 @@
         <v>0.8021</v>
       </c>
       <c r="G5" t="n">
-        <v>103.66711</v>
+        <v>103.66712</v>
       </c>
       <c r="H5" t="n">
         <v>2.87</v>
@@ -640,7 +640,7 @@
         <v>16.00067</v>
       </c>
       <c r="J5" t="n">
-        <v>27.22633</v>
+        <v>27.22632</v>
       </c>
       <c r="K5" t="n">
         <v>11.03523</v>
@@ -654,7 +654,7 @@
         <v>42735</v>
       </c>
       <c r="B6" t="n">
-        <v>26.62235</v>
+        <v>26.62236</v>
       </c>
       <c r="C6" t="n">
         <v>55.55105</v>
@@ -669,7 +669,7 @@
         <v>2.62256</v>
       </c>
       <c r="G6" t="n">
-        <v>113.95856</v>
+        <v>113.95855</v>
       </c>
       <c r="H6" t="n">
         <v>11.34</v>
@@ -678,7 +678,7 @@
         <v>14.246</v>
       </c>
       <c r="J6" t="n">
-        <v>29.61037</v>
+        <v>29.61036</v>
       </c>
       <c r="K6" t="n">
         <v>13.64458</v>
@@ -692,10 +692,10 @@
         <v>43100</v>
       </c>
       <c r="B7" t="n">
-        <v>39.52471</v>
+        <v>39.5247</v>
       </c>
       <c r="C7" t="n">
-        <v>78.17731999999999</v>
+        <v>78.17731000000001</v>
       </c>
       <c r="D7" t="n">
         <v>52.17353</v>
@@ -704,7 +704,7 @@
         <v>58.4735</v>
       </c>
       <c r="F7" t="n">
-        <v>4.77274</v>
+        <v>4.77273</v>
       </c>
       <c r="G7" t="n">
         <v>174.78596</v>
@@ -716,7 +716,7 @@
         <v>20.75667</v>
       </c>
       <c r="J7" t="n">
-        <v>38.75114</v>
+        <v>38.75113</v>
       </c>
       <c r="K7" t="n">
         <v>20.21936</v>
@@ -730,13 +730,13 @@
         <v>43465</v>
       </c>
       <c r="B8" t="n">
-        <v>37.39424</v>
+        <v>37.39425</v>
       </c>
       <c r="C8" t="n">
-        <v>94.43454</v>
+        <v>94.43452000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>51.75552</v>
+        <v>51.75551</v>
       </c>
       <c r="E8" t="n">
         <v>75.0985</v>
@@ -745,7 +745,7 @@
         <v>3.30201</v>
       </c>
       <c r="G8" t="n">
-        <v>129.84639</v>
+        <v>129.84636</v>
       </c>
       <c r="H8" t="n">
         <v>18.46</v>
@@ -754,7 +754,7 @@
         <v>22.18667</v>
       </c>
       <c r="J8" t="n">
-        <v>40.38896</v>
+        <v>40.38894</v>
       </c>
       <c r="K8" t="n">
         <v>20.9517</v>
@@ -768,13 +768,13 @@
         <v>43830</v>
       </c>
       <c r="B9" t="n">
-        <v>70.65937</v>
+        <v>70.65936000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>148.78928</v>
+        <v>148.78926</v>
       </c>
       <c r="D9" t="n">
-        <v>66.33824</v>
+        <v>66.33825</v>
       </c>
       <c r="E9" t="n">
         <v>92.392</v>
@@ -792,7 +792,7 @@
         <v>27.88867</v>
       </c>
       <c r="J9" t="n">
-        <v>52.7932</v>
+        <v>52.79321</v>
       </c>
       <c r="K9" t="n">
         <v>27.03852</v>
@@ -806,10 +806,10 @@
         <v>44196</v>
       </c>
       <c r="B10" t="n">
-        <v>128.81676</v>
+        <v>128.81674</v>
       </c>
       <c r="C10" t="n">
-        <v>212.07539</v>
+        <v>212.07535</v>
       </c>
       <c r="D10" t="n">
         <v>86.80598000000001</v>
@@ -821,7 +821,7 @@
         <v>12.988</v>
       </c>
       <c r="G10" t="n">
-        <v>270.56854</v>
+        <v>270.56857</v>
       </c>
       <c r="H10" t="n">
         <v>91.70999999999999</v>
@@ -844,13 +844,13 @@
         <v>44561</v>
       </c>
       <c r="B11" t="n">
-        <v>173.44945</v>
+        <v>173.44946</v>
       </c>
       <c r="C11" t="n">
-        <v>323.36597</v>
+        <v>323.36594</v>
       </c>
       <c r="D11" t="n">
-        <v>143.48663</v>
+        <v>143.48665</v>
       </c>
       <c r="E11" t="n">
         <v>166.717</v>
@@ -859,7 +859,7 @@
         <v>29.28561</v>
       </c>
       <c r="G11" t="n">
-        <v>333.15909</v>
+        <v>333.15906</v>
       </c>
       <c r="H11" t="n">
         <v>143.89999</v>
@@ -871,7 +871,7 @@
         <v>47.76452</v>
       </c>
       <c r="K11" t="n">
-        <v>61.30046</v>
+        <v>61.30047</v>
       </c>
       <c r="L11" t="n">
         <v>4766.18018</v>
@@ -885,7 +885,7 @@
         <v>127.6515</v>
       </c>
       <c r="C12" t="n">
-        <v>232.74352</v>
+        <v>232.74348</v>
       </c>
       <c r="D12" t="n">
         <v>87.39834999999999</v>
@@ -909,7 +909,7 @@
         <v>25.48586</v>
       </c>
       <c r="K12" t="n">
-        <v>53.16611</v>
+        <v>53.1661</v>
       </c>
       <c r="L12" t="n">
         <v>3839.5</v>
@@ -920,13 +920,13 @@
         <v>45291</v>
       </c>
       <c r="B13" t="n">
-        <v>190.21103</v>
+        <v>190.21104</v>
       </c>
       <c r="C13" t="n">
-        <v>368.1799</v>
+        <v>368.17987</v>
       </c>
       <c r="D13" t="n">
-        <v>138.37328</v>
+        <v>138.37329</v>
       </c>
       <c r="E13" t="n">
         <v>151.94</v>
@@ -935,7 +935,7 @@
         <v>49.37888</v>
       </c>
       <c r="G13" t="n">
-        <v>350.60202</v>
+        <v>350.60199</v>
       </c>
       <c r="H13" t="n">
         <v>147.41</v>
@@ -947,7 +947,7 @@
         <v>49.5859</v>
       </c>
       <c r="K13" t="n">
-        <v>108.55682</v>
+        <v>108.55681</v>
       </c>
       <c r="L13" t="n">
         <v>4769.83008</v>
@@ -964,16 +964,16 @@
         <v>415.77573</v>
       </c>
       <c r="D14" t="n">
-        <v>188.1954</v>
+        <v>188.19543</v>
       </c>
       <c r="E14" t="n">
         <v>219.39</v>
       </c>
       <c r="F14" t="n">
-        <v>133.93987</v>
+        <v>133.93983</v>
       </c>
       <c r="G14" t="n">
-        <v>582.17078</v>
+        <v>582.17084</v>
       </c>
       <c r="H14" t="n">
         <v>120.79</v>
@@ -985,7 +985,7 @@
         <v>20.05</v>
       </c>
       <c r="K14" t="n">
-        <v>228.50441</v>
+        <v>228.50439</v>
       </c>
       <c r="L14" t="n">
         <v>5881.62988</v>
@@ -1011,7 +1011,7 @@
         <v>186.06461</v>
       </c>
       <c r="G15" t="n">
-        <v>658.39502</v>
+        <v>658.39508</v>
       </c>
       <c r="H15" t="n">
         <v>214.16</v>
@@ -1034,37 +1034,37 @@
         <v>46387</v>
       </c>
       <c r="B16" t="n">
-        <v>342.95999</v>
+        <v>333.01999</v>
       </c>
       <c r="C16" t="n">
-        <v>533.6900000000001</v>
+        <v>512.90002</v>
       </c>
       <c r="D16" t="n">
-        <v>347.64001</v>
+        <v>344.07999</v>
       </c>
       <c r="E16" t="n">
-        <v>254.08</v>
+        <v>249.14999</v>
       </c>
       <c r="F16" t="n">
-        <v>221.3</v>
+        <v>228.38</v>
       </c>
       <c r="G16" t="n">
-        <v>737.53998</v>
+        <v>725.17999</v>
       </c>
       <c r="H16" t="n">
-        <v>570.82001</v>
+        <v>611.76001</v>
       </c>
       <c r="I16" t="n">
-        <v>367.16</v>
+        <v>354.81</v>
       </c>
       <c r="J16" t="n">
-        <v>98.12</v>
+        <v>120.23</v>
       </c>
       <c r="K16" t="n">
-        <v>346.25</v>
+        <v>351.19</v>
       </c>
       <c r="L16" t="n">
-        <v>7718.93994</v>
+        <v>7651.54004</v>
       </c>
     </row>
   </sheetData>
@@ -1140,34 +1140,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09836</v>
+        <v>0.09855</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02377</v>
+        <v>0.02324</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03163</v>
+        <v>0.03062</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04501</v>
+        <v>0.04357</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08881</v>
+        <v>0.08562</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06134</v>
+        <v>0.05934</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09561</v>
+        <v>0.09397999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2128</v>
+        <v>0.20576</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05944</v>
+        <v>0.06920999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03858</v>
+        <v>0.03715</v>
       </c>
     </row>
     <row r="3">
@@ -1177,34 +1177,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02377</v>
+        <v>0.02324</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05055</v>
+        <v>0.05173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02268</v>
+        <v>0.02218</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03227</v>
+        <v>0.03157</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06367</v>
+        <v>0.06204</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04397</v>
+        <v>0.04299</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06855</v>
+        <v>0.06809</v>
       </c>
       <c r="I3" t="n">
-        <v>0.15256</v>
+        <v>0.14908</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04262</v>
+        <v>0.05015</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02766</v>
+        <v>0.02691</v>
       </c>
     </row>
     <row r="4">
@@ -1214,34 +1214,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03163</v>
+        <v>0.03062</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02268</v>
+        <v>0.02218</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08951000000000001</v>
+        <v>0.08978999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04293</v>
+        <v>0.04159</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08472</v>
+        <v>0.08173</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05851</v>
+        <v>0.05664</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09121</v>
+        <v>0.08971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.203</v>
+        <v>0.19641</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05671</v>
+        <v>0.06607</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0368</v>
+        <v>0.03546</v>
       </c>
     </row>
     <row r="5">
@@ -1251,34 +1251,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04501</v>
+        <v>0.04357</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03227</v>
+        <v>0.03157</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04293</v>
+        <v>0.04159</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1812</v>
+        <v>0.18188</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12054</v>
+        <v>0.11632</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08325</v>
+        <v>0.08062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.12977</v>
+        <v>0.12768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.28883</v>
+        <v>0.27954</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08068</v>
+        <v>0.09403</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05236</v>
+        <v>0.05047</v>
       </c>
     </row>
     <row r="6">
@@ -1288,34 +1288,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08881</v>
+        <v>0.08562</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06367</v>
+        <v>0.06204</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08472</v>
+        <v>0.08173</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12054</v>
+        <v>0.11632</v>
       </c>
       <c r="F6" t="n">
-        <v>0.70558</v>
+        <v>0.70224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.16428</v>
+        <v>0.15841</v>
       </c>
       <c r="H6" t="n">
-        <v>0.25608</v>
+        <v>0.25088</v>
       </c>
       <c r="I6" t="n">
-        <v>0.56995</v>
+        <v>0.54927</v>
       </c>
       <c r="J6" t="n">
-        <v>0.15921</v>
+        <v>0.18476</v>
       </c>
       <c r="K6" t="n">
-        <v>0.10332</v>
+        <v>0.09916</v>
       </c>
     </row>
     <row r="7">
@@ -1325,34 +1325,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06134</v>
+        <v>0.05934</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04397</v>
+        <v>0.04299</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05851</v>
+        <v>0.05664</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08325</v>
+        <v>0.08062</v>
       </c>
       <c r="F7" t="n">
-        <v>0.16428</v>
+        <v>0.15841</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33654</v>
+        <v>0.3373</v>
       </c>
       <c r="H7" t="n">
-        <v>0.17686</v>
+        <v>0.17387</v>
       </c>
       <c r="I7" t="n">
-        <v>0.39362</v>
+        <v>0.38067</v>
       </c>
       <c r="J7" t="n">
-        <v>0.10995</v>
+        <v>0.12805</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07136000000000001</v>
+        <v>0.06872</v>
       </c>
     </row>
     <row r="8">
@@ -1362,34 +1362,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09561</v>
+        <v>0.09397999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06855</v>
+        <v>0.06809</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09121</v>
+        <v>0.08971</v>
       </c>
       <c r="E8" t="n">
-        <v>0.12977</v>
+        <v>0.12768</v>
       </c>
       <c r="F8" t="n">
-        <v>0.25608</v>
+        <v>0.25088</v>
       </c>
       <c r="G8" t="n">
-        <v>0.17686</v>
+        <v>0.17387</v>
       </c>
       <c r="H8" t="n">
-        <v>0.81779</v>
+        <v>0.84605</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6136</v>
+        <v>0.6029</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1714</v>
+        <v>0.20279</v>
       </c>
       <c r="K8" t="n">
-        <v>0.11124</v>
+        <v>0.10884</v>
       </c>
     </row>
     <row r="9">
@@ -1399,34 +1399,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2128</v>
+        <v>0.20576</v>
       </c>
       <c r="C9" t="n">
-        <v>0.15256</v>
+        <v>0.14908</v>
       </c>
       <c r="D9" t="n">
-        <v>0.203</v>
+        <v>0.19641</v>
       </c>
       <c r="E9" t="n">
-        <v>0.28883</v>
+        <v>0.27954</v>
       </c>
       <c r="F9" t="n">
-        <v>0.56995</v>
+        <v>0.54927</v>
       </c>
       <c r="G9" t="n">
-        <v>0.39362</v>
+        <v>0.38067</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6136</v>
+        <v>0.6029</v>
       </c>
       <c r="I9" t="n">
-        <v>4.051</v>
+        <v>4.05556</v>
       </c>
       <c r="J9" t="n">
-        <v>0.38148</v>
+        <v>0.444</v>
       </c>
       <c r="K9" t="n">
-        <v>0.24757</v>
+        <v>0.2383</v>
       </c>
     </row>
     <row r="10">
@@ -1436,34 +1436,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05944</v>
+        <v>0.06920999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04262</v>
+        <v>0.05015</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05671</v>
+        <v>0.06607</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08068</v>
+        <v>0.09403</v>
       </c>
       <c r="F10" t="n">
-        <v>0.15921</v>
+        <v>0.18476</v>
       </c>
       <c r="G10" t="n">
-        <v>0.10995</v>
+        <v>0.12805</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1714</v>
+        <v>0.20279</v>
       </c>
       <c r="I10" t="n">
-        <v>0.38148</v>
+        <v>0.444</v>
       </c>
       <c r="J10" t="n">
-        <v>0.31609</v>
+        <v>0.45886</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06916</v>
+        <v>0.08016</v>
       </c>
     </row>
     <row r="11">
@@ -1473,34 +1473,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03858</v>
+        <v>0.03715</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02766</v>
+        <v>0.02691</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0368</v>
+        <v>0.03546</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05236</v>
+        <v>0.05047</v>
       </c>
       <c r="F11" t="n">
-        <v>0.10332</v>
+        <v>0.09916</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07136000000000001</v>
+        <v>0.06872</v>
       </c>
       <c r="H11" t="n">
-        <v>0.11124</v>
+        <v>0.10884</v>
       </c>
       <c r="I11" t="n">
-        <v>0.24757</v>
+        <v>0.2383</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06916</v>
+        <v>0.08016</v>
       </c>
       <c r="K11" t="n">
-        <v>0.13313</v>
+        <v>0.13218</v>
       </c>
     </row>
   </sheetData>
@@ -1576,34 +1576,34 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.09855</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.03517</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02964</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.03986</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.09836</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.03399</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.03021</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.04092</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.09843</v>
-      </c>
       <c r="G2" t="n">
-        <v>0.07011000000000001</v>
+        <v>0.07033</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08455</v>
+        <v>0.08093</v>
       </c>
       <c r="I2" t="n">
-        <v>0.24486</v>
+        <v>0.24592</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04773</v>
+        <v>0.04959</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03878</v>
+        <v>0.03846</v>
       </c>
     </row>
     <row r="3">
@@ -1613,34 +1613,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03399</v>
+        <v>0.03517</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05055</v>
+        <v>0.05173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03106</v>
+        <v>0.03207</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03838</v>
+        <v>0.03912</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07226</v>
+        <v>0.07292</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0621</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06173</v>
+        <v>0.05823</v>
       </c>
       <c r="I3" t="n">
-        <v>0.16167</v>
+        <v>0.16239</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03758</v>
+        <v>0.03584</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03212</v>
+        <v>0.03274</v>
       </c>
     </row>
     <row r="4">
@@ -1650,34 +1650,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03021</v>
+        <v>0.02964</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03106</v>
+        <v>0.03207</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08951000000000001</v>
+        <v>0.08978999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0546</v>
+        <v>0.05541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09311</v>
+        <v>0.09239</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07704999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06562999999999999</v>
+        <v>0.06033</v>
       </c>
       <c r="I4" t="n">
-        <v>0.18643</v>
+        <v>0.18109</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04998</v>
+        <v>0.05103</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04584</v>
+        <v>0.04624</v>
       </c>
     </row>
     <row r="5">
@@ -1687,34 +1687,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04092</v>
+        <v>0.03986</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03838</v>
+        <v>0.03912</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0546</v>
+        <v>0.05541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1812</v>
+        <v>0.18188</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1298</v>
+        <v>0.12859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.10541</v>
+        <v>0.10686</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09186999999999999</v>
+        <v>0.08412</v>
       </c>
       <c r="I5" t="n">
-        <v>0.31821</v>
+        <v>0.31726</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04984</v>
+        <v>0.04886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05397</v>
+        <v>0.05326</v>
       </c>
     </row>
     <row r="6">
@@ -1724,34 +1724,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09843</v>
+        <v>0.09836</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07226</v>
+        <v>0.07292</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09311</v>
+        <v>0.09239</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1298</v>
+        <v>0.12859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.70558</v>
+        <v>0.70224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.21442</v>
+        <v>0.21709</v>
       </c>
       <c r="H6" t="n">
-        <v>0.29343</v>
+        <v>0.29261</v>
       </c>
       <c r="I6" t="n">
-        <v>0.46727</v>
+        <v>0.44191</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09505</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.12761</v>
+        <v>0.12734</v>
       </c>
     </row>
     <row r="7">
@@ -1761,34 +1761,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07011000000000001</v>
+        <v>0.07033</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0621</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07704999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="E7" t="n">
-        <v>0.10541</v>
+        <v>0.10686</v>
       </c>
       <c r="F7" t="n">
-        <v>0.21442</v>
+        <v>0.21709</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33654</v>
+        <v>0.3373</v>
       </c>
       <c r="H7" t="n">
-        <v>0.13543</v>
+        <v>0.12647</v>
       </c>
       <c r="I7" t="n">
-        <v>0.36002</v>
+        <v>0.34924</v>
       </c>
       <c r="J7" t="n">
-        <v>0.10544</v>
+        <v>0.1095</v>
       </c>
       <c r="K7" t="n">
-        <v>0.10513</v>
+        <v>0.10783</v>
       </c>
     </row>
     <row r="8">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08455</v>
+        <v>0.08093</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06173</v>
+        <v>0.05823</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06562999999999999</v>
+        <v>0.06033</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09186999999999999</v>
+        <v>0.08412</v>
       </c>
       <c r="F8" t="n">
-        <v>0.29343</v>
+        <v>0.29261</v>
       </c>
       <c r="G8" t="n">
-        <v>0.13543</v>
+        <v>0.12647</v>
       </c>
       <c r="H8" t="n">
-        <v>0.81779</v>
+        <v>0.84605</v>
       </c>
       <c r="I8" t="n">
-        <v>0.42212</v>
+        <v>0.38521</v>
       </c>
       <c r="J8" t="n">
-        <v>0.18538</v>
+        <v>0.23327</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03987</v>
+        <v>0.02762</v>
       </c>
     </row>
     <row r="9">
@@ -1835,34 +1835,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.24486</v>
+        <v>0.24592</v>
       </c>
       <c r="C9" t="n">
-        <v>0.16167</v>
+        <v>0.16239</v>
       </c>
       <c r="D9" t="n">
-        <v>0.18643</v>
+        <v>0.18109</v>
       </c>
       <c r="E9" t="n">
-        <v>0.31821</v>
+        <v>0.31726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.46727</v>
+        <v>0.44191</v>
       </c>
       <c r="G9" t="n">
-        <v>0.36002</v>
+        <v>0.34924</v>
       </c>
       <c r="H9" t="n">
-        <v>0.42212</v>
+        <v>0.38521</v>
       </c>
       <c r="I9" t="n">
-        <v>4.051</v>
+        <v>4.05556</v>
       </c>
       <c r="J9" t="n">
-        <v>0.17324</v>
+        <v>0.16254</v>
       </c>
       <c r="K9" t="n">
-        <v>0.21517</v>
+        <v>0.2057</v>
       </c>
     </row>
     <row r="10">
@@ -1872,34 +1872,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04773</v>
+        <v>0.04959</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03758</v>
+        <v>0.03584</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04998</v>
+        <v>0.05103</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04984</v>
+        <v>0.04886</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09505</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.10544</v>
+        <v>0.1095</v>
       </c>
       <c r="H10" t="n">
-        <v>0.18538</v>
+        <v>0.23327</v>
       </c>
       <c r="I10" t="n">
-        <v>0.17324</v>
+        <v>0.16254</v>
       </c>
       <c r="J10" t="n">
-        <v>0.31609</v>
+        <v>0.45886</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04019</v>
+        <v>0.03556</v>
       </c>
     </row>
     <row r="11">
@@ -1909,34 +1909,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03878</v>
+        <v>0.03846</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03212</v>
+        <v>0.03274</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04584</v>
+        <v>0.04624</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05397</v>
+        <v>0.05326</v>
       </c>
       <c r="F11" t="n">
-        <v>0.12761</v>
+        <v>0.12734</v>
       </c>
       <c r="G11" t="n">
-        <v>0.10513</v>
+        <v>0.10783</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03987</v>
+        <v>0.02762</v>
       </c>
       <c r="I11" t="n">
-        <v>0.21517</v>
+        <v>0.2057</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04019</v>
+        <v>0.03556</v>
       </c>
       <c r="K11" t="n">
-        <v>0.13313</v>
+        <v>0.13218</v>
       </c>
     </row>
   </sheetData>
@@ -2012,34 +2012,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09836</v>
+        <v>0.09855</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03812</v>
+        <v>0.03844</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04719</v>
+        <v>0.04744</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02764</v>
+        <v>0.02795</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09622</v>
+        <v>0.09694</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08808000000000001</v>
+        <v>0.08851000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04824</v>
+        <v>0.04686</v>
       </c>
       <c r="I2" t="n">
-        <v>0.13563</v>
+        <v>0.13709</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0335</v>
+        <v>0.03075</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04852</v>
+        <v>0.04906</v>
       </c>
     </row>
     <row r="3">
@@ -2049,34 +2049,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03812</v>
+        <v>0.03844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05055</v>
+        <v>0.05173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03944</v>
+        <v>0.03986</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02311</v>
+        <v>0.02349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08043</v>
+        <v>0.08144</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07362</v>
+        <v>0.07437000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04033</v>
+        <v>0.03937</v>
       </c>
       <c r="I3" t="n">
-        <v>0.11337</v>
+        <v>0.11518</v>
       </c>
       <c r="J3" t="n">
-        <v>0.028</v>
+        <v>0.02584</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04056</v>
+        <v>0.04122</v>
       </c>
     </row>
     <row r="4">
@@ -2086,34 +2086,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04719</v>
+        <v>0.04744</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03944</v>
+        <v>0.03986</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08951000000000001</v>
+        <v>0.08978999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0286</v>
+        <v>0.02899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09956</v>
+        <v>0.10052</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09113</v>
+        <v>0.09179</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04992</v>
+        <v>0.04859</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14033</v>
+        <v>0.14216</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03466</v>
+        <v>0.03189</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0502</v>
+        <v>0.05087</v>
       </c>
     </row>
     <row r="5">
@@ -2123,34 +2123,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02764</v>
+        <v>0.02795</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02311</v>
+        <v>0.02349</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0286</v>
+        <v>0.02899</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1812</v>
+        <v>0.18188</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05832</v>
+        <v>0.05923</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05339</v>
+        <v>0.05408</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02924</v>
+        <v>0.02863</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08221000000000001</v>
+        <v>0.08376</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0203</v>
+        <v>0.01879</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02941</v>
+        <v>0.02998</v>
       </c>
     </row>
     <row r="6">
@@ -2160,34 +2160,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09622</v>
+        <v>0.09694</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08043</v>
+        <v>0.08144</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09956</v>
+        <v>0.10052</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05832</v>
+        <v>0.05923</v>
       </c>
       <c r="F6" t="n">
-        <v>0.70558</v>
+        <v>0.70224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.18585</v>
+        <v>0.18755</v>
       </c>
       <c r="H6" t="n">
-        <v>0.10179</v>
+        <v>0.09927999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.28616</v>
+        <v>0.29046</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07068000000000001</v>
+        <v>0.06516</v>
       </c>
       <c r="K6" t="n">
-        <v>0.10238</v>
+        <v>0.10395</v>
       </c>
     </row>
     <row r="7">
@@ -2197,34 +2197,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08808000000000001</v>
+        <v>0.08851000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07362</v>
+        <v>0.07437000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09113</v>
+        <v>0.09179</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05339</v>
+        <v>0.05408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.18585</v>
+        <v>0.18755</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33654</v>
+        <v>0.3373</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09318</v>
+        <v>0.09066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.26195</v>
+        <v>0.26523</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0595</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09372</v>
+        <v>0.09492</v>
       </c>
     </row>
     <row r="8">
@@ -2234,34 +2234,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04824</v>
+        <v>0.04686</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04033</v>
+        <v>0.03937</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04992</v>
+        <v>0.04859</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02924</v>
+        <v>0.02863</v>
       </c>
       <c r="F8" t="n">
-        <v>0.10179</v>
+        <v>0.09927999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09318</v>
+        <v>0.09066</v>
       </c>
       <c r="H8" t="n">
-        <v>0.81779</v>
+        <v>0.84605</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14348</v>
+        <v>0.1404</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03544</v>
+        <v>0.0315</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05133</v>
+        <v>0.05025</v>
       </c>
     </row>
     <row r="9">
@@ -2271,34 +2271,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.13563</v>
+        <v>0.13709</v>
       </c>
       <c r="C9" t="n">
-        <v>0.11337</v>
+        <v>0.11518</v>
       </c>
       <c r="D9" t="n">
-        <v>0.14033</v>
+        <v>0.14216</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08221000000000001</v>
+        <v>0.08376</v>
       </c>
       <c r="F9" t="n">
-        <v>0.28616</v>
+        <v>0.29046</v>
       </c>
       <c r="G9" t="n">
-        <v>0.26195</v>
+        <v>0.26523</v>
       </c>
       <c r="H9" t="n">
-        <v>0.14348</v>
+        <v>0.1404</v>
       </c>
       <c r="I9" t="n">
-        <v>4.051</v>
+        <v>4.05556</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09962</v>
+        <v>0.09214</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1443</v>
+        <v>0.14701</v>
       </c>
     </row>
     <row r="10">
@@ -2308,34 +2308,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0335</v>
+        <v>0.03075</v>
       </c>
       <c r="C10" t="n">
-        <v>0.028</v>
+        <v>0.02584</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03466</v>
+        <v>0.03189</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0203</v>
+        <v>0.01879</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07068000000000001</v>
+        <v>0.06516</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0595</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03544</v>
+        <v>0.0315</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09962</v>
+        <v>0.09214</v>
       </c>
       <c r="J10" t="n">
-        <v>0.31609</v>
+        <v>0.45886</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03564</v>
+        <v>0.03298</v>
       </c>
     </row>
     <row r="11">
@@ -2345,34 +2345,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04852</v>
+        <v>0.04906</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04056</v>
+        <v>0.04122</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0502</v>
+        <v>0.05087</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02941</v>
+        <v>0.02998</v>
       </c>
       <c r="F11" t="n">
-        <v>0.10238</v>
+        <v>0.10395</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09372</v>
+        <v>0.09492</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05133</v>
+        <v>0.05025</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1443</v>
+        <v>0.14701</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03564</v>
+        <v>0.03298</v>
       </c>
       <c r="K11" t="n">
-        <v>0.13313</v>
+        <v>0.13218</v>
       </c>
     </row>
   </sheetData>
@@ -2448,34 +2448,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09836</v>
+        <v>0.09855</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03812</v>
+        <v>0.03844</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04719</v>
+        <v>0.04744</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02764</v>
+        <v>0.02795</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09622</v>
+        <v>0.09694</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08808000000000001</v>
+        <v>0.08851000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04824</v>
+        <v>0.04686</v>
       </c>
       <c r="I2" t="n">
-        <v>0.13563</v>
+        <v>0.13709</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0335</v>
+        <v>0.03075</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04852</v>
+        <v>0.04906</v>
       </c>
     </row>
     <row r="3">
@@ -2485,34 +2485,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03812</v>
+        <v>0.03844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05055</v>
+        <v>0.05173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03944</v>
+        <v>0.03986</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02311</v>
+        <v>0.02349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08043</v>
+        <v>0.08144</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07362</v>
+        <v>0.07437000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04033</v>
+        <v>0.03937</v>
       </c>
       <c r="I3" t="n">
-        <v>0.11337</v>
+        <v>0.11518</v>
       </c>
       <c r="J3" t="n">
-        <v>0.028</v>
+        <v>0.02584</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04056</v>
+        <v>0.04122</v>
       </c>
     </row>
     <row r="4">
@@ -2522,34 +2522,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04719</v>
+        <v>0.04744</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03944</v>
+        <v>0.03986</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08951000000000001</v>
+        <v>0.08978999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0286</v>
+        <v>0.02899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09956</v>
+        <v>0.10052</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09113</v>
+        <v>0.09179</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04992</v>
+        <v>0.04859</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14033</v>
+        <v>0.14216</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03466</v>
+        <v>0.03189</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0502</v>
+        <v>0.05087</v>
       </c>
     </row>
     <row r="5">
@@ -2559,34 +2559,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02764</v>
+        <v>0.02795</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02311</v>
+        <v>0.02349</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0286</v>
+        <v>0.02899</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1812</v>
+        <v>0.18188</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05832</v>
+        <v>0.05923</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05339</v>
+        <v>0.05408</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02924</v>
+        <v>0.02863</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08221000000000001</v>
+        <v>0.08376</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0203</v>
+        <v>0.01879</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02941</v>
+        <v>0.02998</v>
       </c>
     </row>
     <row r="6">
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09622</v>
+        <v>0.09694</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08043</v>
+        <v>0.08144</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09956</v>
+        <v>0.10052</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05832</v>
+        <v>0.05923</v>
       </c>
       <c r="F6" t="n">
-        <v>0.70558</v>
+        <v>0.70224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.18585</v>
+        <v>0.18755</v>
       </c>
       <c r="H6" t="n">
-        <v>0.10179</v>
+        <v>0.09927999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.28616</v>
+        <v>0.29046</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07068000000000001</v>
+        <v>0.06516</v>
       </c>
       <c r="K6" t="n">
-        <v>0.10238</v>
+        <v>0.10395</v>
       </c>
     </row>
     <row r="7">
@@ -2633,34 +2633,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08808000000000001</v>
+        <v>0.08851000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07362</v>
+        <v>0.07437000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09113</v>
+        <v>0.09179</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05339</v>
+        <v>0.05408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.18585</v>
+        <v>0.18755</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33654</v>
+        <v>0.3373</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09318</v>
+        <v>0.09066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.26195</v>
+        <v>0.26523</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0595</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09372</v>
+        <v>0.09492</v>
       </c>
     </row>
     <row r="8">
@@ -2670,34 +2670,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04824</v>
+        <v>0.04686</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04033</v>
+        <v>0.03937</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04992</v>
+        <v>0.04859</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02924</v>
+        <v>0.02863</v>
       </c>
       <c r="F8" t="n">
-        <v>0.10179</v>
+        <v>0.09927999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09318</v>
+        <v>0.09066</v>
       </c>
       <c r="H8" t="n">
-        <v>0.81779</v>
+        <v>0.84605</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14348</v>
+        <v>0.1404</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03544</v>
+        <v>0.0315</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05133</v>
+        <v>0.05025</v>
       </c>
     </row>
     <row r="9">
@@ -2707,34 +2707,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.13563</v>
+        <v>0.13709</v>
       </c>
       <c r="C9" t="n">
-        <v>0.11337</v>
+        <v>0.11518</v>
       </c>
       <c r="D9" t="n">
-        <v>0.14033</v>
+        <v>0.14216</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08221000000000001</v>
+        <v>0.08376</v>
       </c>
       <c r="F9" t="n">
-        <v>0.28616</v>
+        <v>0.29046</v>
       </c>
       <c r="G9" t="n">
-        <v>0.26195</v>
+        <v>0.26523</v>
       </c>
       <c r="H9" t="n">
-        <v>0.14348</v>
+        <v>0.1404</v>
       </c>
       <c r="I9" t="n">
-        <v>4.051</v>
+        <v>4.05556</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09962</v>
+        <v>0.09214</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1443</v>
+        <v>0.14701</v>
       </c>
     </row>
     <row r="10">
@@ -2744,34 +2744,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0335</v>
+        <v>0.03075</v>
       </c>
       <c r="C10" t="n">
-        <v>0.028</v>
+        <v>0.02584</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03466</v>
+        <v>0.03189</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0203</v>
+        <v>0.01879</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07068000000000001</v>
+        <v>0.06516</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0595</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03544</v>
+        <v>0.0315</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09962</v>
+        <v>0.09214</v>
       </c>
       <c r="J10" t="n">
-        <v>0.31609</v>
+        <v>0.45886</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03564</v>
+        <v>0.03298</v>
       </c>
     </row>
     <row r="11">
@@ -2781,34 +2781,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04852</v>
+        <v>0.04906</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04056</v>
+        <v>0.04122</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0502</v>
+        <v>0.05087</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02941</v>
+        <v>0.02998</v>
       </c>
       <c r="F11" t="n">
-        <v>0.10238</v>
+        <v>0.10395</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09372</v>
+        <v>0.09492</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05133</v>
+        <v>0.05025</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1443</v>
+        <v>0.14701</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03564</v>
+        <v>0.03298</v>
       </c>
       <c r="K11" t="n">
-        <v>0.13313</v>
+        <v>0.13218</v>
       </c>
     </row>
   </sheetData>
@@ -2884,34 +2884,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.13186</v>
+        <v>0.138</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03513</v>
+        <v>0.03811</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02137</v>
+        <v>0.02029</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03249</v>
+        <v>0.04897</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.09969</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.07975</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04922</v>
+        <v>0.03685</v>
       </c>
       <c r="I2" t="n">
-        <v>0.29813</v>
+        <v>0.29728</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04679</v>
+        <v>0.03892</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04694</v>
+        <v>0.04349</v>
       </c>
     </row>
     <row r="3">
@@ -2921,34 +2921,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03513</v>
+        <v>0.03811</v>
       </c>
       <c r="C3" t="n">
-        <v>0.10323</v>
+        <v>0.09911</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05354</v>
+        <v>0.05471</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0432</v>
+        <v>0.04775</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06315</v>
+        <v>0.07184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09908</v>
+        <v>0.09415999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0351</v>
+        <v>0.01704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.17761</v>
+        <v>0.18005</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05025</v>
+        <v>0.0409</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04058</v>
+        <v>0.04245</v>
       </c>
     </row>
     <row r="4">
@@ -2958,34 +2958,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02137</v>
+        <v>0.02029</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05354</v>
+        <v>0.05471</v>
       </c>
       <c r="D4" t="n">
-        <v>0.16581</v>
+        <v>0.18152</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06612</v>
+        <v>0.05854</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07153</v>
+        <v>0.07643</v>
       </c>
       <c r="G4" t="n">
-        <v>0.11964</v>
+        <v>0.11529</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00919</v>
+        <v>-0.01062</v>
       </c>
       <c r="I4" t="n">
-        <v>0.15815</v>
+        <v>0.159</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06038</v>
+        <v>0.06541</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06033</v>
+        <v>0.07052</v>
       </c>
     </row>
     <row r="5">
@@ -2995,34 +2995,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03249</v>
+        <v>0.04897</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0432</v>
+        <v>0.04775</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06612</v>
+        <v>0.05854</v>
       </c>
       <c r="E5" t="n">
-        <v>0.24269</v>
+        <v>0.22164</v>
       </c>
       <c r="F5" t="n">
-        <v>0.11779</v>
+        <v>0.11793</v>
       </c>
       <c r="G5" t="n">
-        <v>0.14041</v>
+        <v>0.14974</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01298</v>
+        <v>-0.00513</v>
       </c>
       <c r="I5" t="n">
-        <v>0.36348</v>
+        <v>0.36323</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01692</v>
+        <v>0.01534</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0612</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -3032,34 +3032,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.09969</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06315</v>
+        <v>0.07184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07153</v>
+        <v>0.07643</v>
       </c>
       <c r="E6" t="n">
-        <v>0.11779</v>
+        <v>0.11793</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7174</v>
+        <v>0.68363</v>
       </c>
       <c r="G6" t="n">
-        <v>0.21944</v>
+        <v>0.21918</v>
       </c>
       <c r="H6" t="n">
-        <v>0.28473</v>
+        <v>0.28672</v>
       </c>
       <c r="I6" t="n">
-        <v>0.30277</v>
+        <v>0.29732</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.11379</v>
+        <v>-0.14406</v>
       </c>
       <c r="K6" t="n">
-        <v>0.13565</v>
+        <v>0.12476</v>
       </c>
     </row>
     <row r="7">
@@ -3069,34 +3069,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.07975</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09908</v>
+        <v>0.09415999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.11964</v>
+        <v>0.11529</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14041</v>
+        <v>0.14974</v>
       </c>
       <c r="F7" t="n">
-        <v>0.21944</v>
+        <v>0.21918</v>
       </c>
       <c r="G7" t="n">
-        <v>0.40981</v>
+        <v>0.42726</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02</v>
+        <v>-0.02318</v>
       </c>
       <c r="I7" t="n">
-        <v>0.30556</v>
+        <v>0.30555</v>
       </c>
       <c r="J7" t="n">
-        <v>0.15901</v>
+        <v>0.17076</v>
       </c>
       <c r="K7" t="n">
-        <v>0.15059</v>
+        <v>0.16305</v>
       </c>
     </row>
     <row r="8">
@@ -3106,34 +3106,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04922</v>
+        <v>0.03685</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0351</v>
+        <v>0.01704</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00919</v>
+        <v>-0.01062</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01298</v>
+        <v>-0.00513</v>
       </c>
       <c r="F8" t="n">
-        <v>0.28473</v>
+        <v>0.28672</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02</v>
+        <v>-0.02318</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77591</v>
+        <v>0.79216</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1108</v>
+        <v>0.09426</v>
       </c>
       <c r="J8" t="n">
-        <v>0.15865</v>
+        <v>0.16059</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.08112</v>
+        <v>-0.09685000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -3143,34 +3143,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.29813</v>
+        <v>0.29728</v>
       </c>
       <c r="C9" t="n">
-        <v>0.17761</v>
+        <v>0.18005</v>
       </c>
       <c r="D9" t="n">
-        <v>0.15815</v>
+        <v>0.159</v>
       </c>
       <c r="E9" t="n">
-        <v>0.36348</v>
+        <v>0.36323</v>
       </c>
       <c r="F9" t="n">
-        <v>0.30277</v>
+        <v>0.29732</v>
       </c>
       <c r="G9" t="n">
-        <v>0.30556</v>
+        <v>0.30555</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1108</v>
+        <v>0.09426</v>
       </c>
       <c r="I9" t="n">
-        <v>4.01404</v>
+        <v>3.98597</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.17146</v>
+        <v>-0.22128</v>
       </c>
       <c r="K9" t="n">
-        <v>0.15827</v>
+        <v>0.1564</v>
       </c>
     </row>
     <row r="10">
@@ -3180,34 +3180,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04679</v>
+        <v>0.03892</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05025</v>
+        <v>0.0409</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06038</v>
+        <v>0.06541</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01692</v>
+        <v>0.01534</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.11379</v>
+        <v>-0.14406</v>
       </c>
       <c r="G10" t="n">
-        <v>0.15901</v>
+        <v>0.17076</v>
       </c>
       <c r="H10" t="n">
-        <v>0.15865</v>
+        <v>0.16059</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.17146</v>
+        <v>-0.22128</v>
       </c>
       <c r="J10" t="n">
-        <v>0.49526</v>
+        <v>0.64615</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00191</v>
+        <v>0.00788</v>
       </c>
     </row>
     <row r="11">
@@ -3217,34 +3217,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04694</v>
+        <v>0.04349</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04058</v>
+        <v>0.04245</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06033</v>
+        <v>0.07052</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0612</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.13565</v>
+        <v>0.12476</v>
       </c>
       <c r="G11" t="n">
-        <v>0.15059</v>
+        <v>0.16305</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.08112</v>
+        <v>-0.09685000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.15827</v>
+        <v>0.1564</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00191</v>
+        <v>0.00788</v>
       </c>
       <c r="K11" t="n">
-        <v>0.21399</v>
+        <v>0.22098</v>
       </c>
     </row>
   </sheetData>
@@ -3303,19 +3303,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1385</v>
+        <v>0.13759</v>
       </c>
       <c r="D2" t="n">
-        <v>0.16974</v>
+        <v>0.17314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14547</v>
+        <v>0.14871</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0948</v>
+        <v>0.10213</v>
       </c>
       <c r="G2" t="n">
-        <v>0.26014</v>
+        <v>0.23477</v>
       </c>
     </row>
     <row r="3">
@@ -3325,22 +3325,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.77475</v>
+        <v>0.76622</v>
       </c>
       <c r="C3" t="n">
-        <v>0.14293</v>
+        <v>0.14272</v>
       </c>
       <c r="D3" t="n">
-        <v>0.37504</v>
+        <v>0.37254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.58843</v>
+        <v>0.57435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.60549</v>
+        <v>0.59666</v>
       </c>
       <c r="G3" t="n">
-        <v>0.31071</v>
+        <v>0.33864</v>
       </c>
     </row>
     <row r="4">
@@ -3350,22 +3350,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00861</v>
+        <v>0.00512</v>
       </c>
       <c r="C4" t="n">
-        <v>0.13506</v>
+        <v>0.135</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1741</v>
+        <v>0.17939</v>
       </c>
       <c r="E4" t="n">
-        <v>0.18723</v>
+        <v>0.18893</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09014</v>
+        <v>0.09744999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.13941</v>
+        <v>0.1275</v>
       </c>
     </row>
     <row r="5">
@@ -3375,22 +3375,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01224</v>
+        <v>0.01386</v>
       </c>
       <c r="C5" t="n">
-        <v>0.12376</v>
+        <v>0.12377</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07306</v>
+        <v>0.07467</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00063</v>
+        <v>0.00313</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12258</v>
+        <v>0.12437</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0861</v>
+        <v>0.0737</v>
       </c>
     </row>
     <row r="6">
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04301</v>
+        <v>0.04717</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0682</v>
+        <v>0.07131999999999999</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -3450,22 +3450,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00146</v>
+        <v>0.00113</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07929</v>
+        <v>0.07776</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01861</v>
+        <v>0.01993</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00362</v>
+        <v>0.00558</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05133</v>
+        <v>0.07152</v>
       </c>
     </row>
     <row r="9">
@@ -3478,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00732</v>
+        <v>0.009509999999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -3500,22 +3500,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08056000000000001</v>
+        <v>0.08391</v>
       </c>
       <c r="C10" t="n">
-        <v>0.12409</v>
+        <v>0.11717</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06336</v>
+        <v>0.05076</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00539</v>
+        <v>0.00745</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05221</v>
+        <v>0.04136</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02953</v>
+        <v>0.02438</v>
       </c>
     </row>
     <row r="11">
@@ -3525,22 +3525,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.12238</v>
+        <v>0.12976</v>
       </c>
       <c r="C11" t="n">
-        <v>0.13783</v>
+        <v>0.138</v>
       </c>
       <c r="D11" t="n">
-        <v>0.12609</v>
+        <v>0.12957</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07285999999999999</v>
+        <v>0.07743999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03116</v>
+        <v>0.03245</v>
       </c>
       <c r="G11" t="n">
-        <v>0.12278</v>
+        <v>0.1295</v>
       </c>
     </row>
   </sheetData>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.21777</v>
+        <v>0.21736</v>
       </c>
     </row>
     <row r="3">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2822</v>
+        <v>0.28511</v>
       </c>
     </row>
     <row r="4">
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.16915</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="5">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.20754</v>
+        <v>0.20958</v>
       </c>
     </row>
     <row r="6">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.20853</v>
+        <v>0.21029</v>
       </c>
     </row>
     <row r="7">
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2463</v>
+        <v>0.24641</v>
       </c>
     </row>
   </sheetData>
@@ -3899,7 +3899,7 @@
         <v>0.06889000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04227</v>
+        <v>0.04226</v>
       </c>
       <c r="K7" t="n">
         <v>0.03622</v>
@@ -4155,34 +4155,34 @@
         <v>46387</v>
       </c>
       <c r="B15" t="n">
-        <v>0.26497</v>
+        <v>0.2283</v>
       </c>
       <c r="C15" t="n">
-        <v>0.11053</v>
+        <v>0.06727</v>
       </c>
       <c r="D15" t="n">
-        <v>0.11283</v>
+        <v>0.10144</v>
       </c>
       <c r="E15" t="n">
-        <v>0.10077</v>
+        <v>0.07940999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.18937</v>
+        <v>0.22742</v>
       </c>
       <c r="G15" t="n">
-        <v>0.12021</v>
+        <v>0.10144</v>
       </c>
       <c r="H15" t="n">
-        <v>1.66539</v>
+        <v>1.85656</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.18358</v>
+        <v>-0.21104</v>
       </c>
       <c r="J15" t="n">
-        <v>1.65908</v>
+        <v>2.25827</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00595</v>
+        <v>0.0203</v>
       </c>
     </row>
   </sheetData>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2829</v>
+        <v>0.2802</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3255</v>
+        <v>0.3258</v>
       </c>
       <c r="D2" t="n">
         <v>-0.264</v>
@@ -4255,10 +4255,10 @@
         <v>0.8895999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3865</v>
+        <v>0.4132</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1329</v>
+        <v>-0.129</v>
       </c>
     </row>
     <row r="3">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.281</v>
+        <v>0.278</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2333</v>
+        <v>0.236</v>
       </c>
       <c r="D3" t="n">
         <v>-0.2802</v>
@@ -4280,10 +4280,10 @@
         <v>0.5819</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8017</v>
+        <v>-0.7614</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1888</v>
+        <v>0.9554</v>
       </c>
     </row>
     <row r="4">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2789</v>
+        <v>0.2781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3105</v>
+        <v>0.311</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3909</v>
@@ -4305,10 +4305,10 @@
         <v>0.6599</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6347</v>
+        <v>-0.6256</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1182</v>
       </c>
     </row>
     <row r="5">
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3161</v>
+        <v>0.3146</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4417</v>
+        <v>0.4426</v>
       </c>
       <c r="D5" t="n">
         <v>-0.4962</v>
@@ -4330,10 +4330,10 @@
         <v>1.1778</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1367</v>
+        <v>0.1446</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0247</v>
       </c>
     </row>
     <row r="6">
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8205</v>
+        <v>0.8232</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8717</v>
+        <v>0.8696</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5026</v>
@@ -4355,10 +4355,10 @@
         <v>2.3902</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4606</v>
+        <v>0.4588</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4071</v>
+        <v>-0.3898</v>
       </c>
     </row>
     <row r="7">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3955</v>
+        <v>0.3941</v>
       </c>
       <c r="C7" t="n">
-        <v>0.602</v>
+        <v>0.6027</v>
       </c>
       <c r="D7" t="n">
         <v>-0.6422</v>
@@ -4380,10 +4380,10 @@
         <v>1.9413</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0443</v>
+        <v>1.0467</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9263</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="8">
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7191</v>
+        <v>0.7328</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9385</v>
+        <v>0.9545</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5499000000000001</v>
@@ -4405,10 +4405,10 @@
         <v>2.9512</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8622</v>
+        <v>0.8337</v>
       </c>
       <c r="G8" t="n">
-        <v>1.058</v>
+        <v>0.7977</v>
       </c>
     </row>
     <row r="9">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>2.0887</v>
+        <v>2.0899</v>
       </c>
       <c r="D9" t="n">
         <v>-0.6503</v>
@@ -4430,10 +4430,10 @@
         <v>7.4344</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7183</v>
+        <v>2.7159</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7335</v>
+        <v>7.7225</v>
       </c>
     </row>
     <row r="10">
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2694</v>
+        <v>0.3122</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5834</v>
+        <v>0.703</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5957</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6591</v>
+        <v>2.2583</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9105</v>
+        <v>1.6463</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3783</v>
+        <v>4.026</v>
       </c>
     </row>
     <row r="11">
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4775</v>
+        <v>0.4785</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3786</v>
+        <v>0.3773</v>
       </c>
       <c r="D11" t="n">
         <v>-0.1327</v>
@@ -4480,10 +4480,10 @@
         <v>1.1049</v>
       </c>
       <c r="F11" t="n">
-        <v>0.157</v>
+        <v>0.1648</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6701</v>
+        <v>-0.6615</v>
       </c>
     </row>
   </sheetData>
@@ -4559,34 +4559,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09836</v>
+        <v>0.09855</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05137</v>
+        <v>0.05198</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02779</v>
+        <v>0.02827</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03398</v>
+        <v>0.03462</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1148</v>
+        <v>0.11631</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08502999999999999</v>
+        <v>0.08581999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06574000000000001</v>
+        <v>0.06254999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2994</v>
+        <v>0.30251</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02781</v>
+        <v>0.02195</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03914</v>
+        <v>0.04032</v>
       </c>
     </row>
     <row r="3">
@@ -4596,34 +4596,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05137</v>
+        <v>0.05198</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05055</v>
+        <v>0.05173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04532</v>
+        <v>0.046</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04878</v>
+        <v>0.04977</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08687</v>
+        <v>0.08825</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09293999999999999</v>
+        <v>0.09407</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05013</v>
+        <v>0.04432</v>
       </c>
       <c r="I3" t="n">
-        <v>0.17717</v>
+        <v>0.18114</v>
       </c>
       <c r="J3" t="n">
-        <v>0.029</v>
+        <v>0.01569</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0397</v>
+        <v>0.04094</v>
       </c>
     </row>
     <row r="4">
@@ -4633,34 +4633,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02779</v>
+        <v>0.02827</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04532</v>
+        <v>0.046</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08951000000000001</v>
+        <v>0.08978999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07445</v>
+        <v>0.07489</v>
       </c>
       <c r="F4" t="n">
-        <v>0.10738</v>
+        <v>0.10741</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1086</v>
+        <v>0.10906</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02211</v>
+        <v>0.01893</v>
       </c>
       <c r="I4" t="n">
-        <v>0.15822</v>
+        <v>0.1595</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03853</v>
+        <v>0.02984</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06123</v>
+        <v>0.06143</v>
       </c>
     </row>
     <row r="5">
@@ -4670,34 +4670,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03398</v>
+        <v>0.03462</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04878</v>
+        <v>0.04977</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07445</v>
+        <v>0.07489</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1812</v>
+        <v>0.18188</v>
       </c>
       <c r="F5" t="n">
-        <v>0.14556</v>
+        <v>0.14588</v>
       </c>
       <c r="G5" t="n">
-        <v>0.14312</v>
+        <v>0.14385</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02738</v>
+        <v>0.02273</v>
       </c>
       <c r="I5" t="n">
-        <v>0.36819</v>
+        <v>0.37041</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.00262</v>
+        <v>-0.0148</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05671</v>
+        <v>0.05719</v>
       </c>
     </row>
     <row r="6">
@@ -4707,34 +4707,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1148</v>
+        <v>0.11631</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08687</v>
+        <v>0.08825</v>
       </c>
       <c r="D6" t="n">
-        <v>0.10738</v>
+        <v>0.10741</v>
       </c>
       <c r="E6" t="n">
-        <v>0.14556</v>
+        <v>0.14588</v>
       </c>
       <c r="F6" t="n">
-        <v>0.70558</v>
+        <v>0.70224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.29974</v>
+        <v>0.29979</v>
       </c>
       <c r="H6" t="n">
-        <v>0.35699</v>
+        <v>0.35142</v>
       </c>
       <c r="I6" t="n">
-        <v>0.29257</v>
+        <v>0.29062</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.01411</v>
+        <v>-0.03583</v>
       </c>
       <c r="K6" t="n">
-        <v>0.16894</v>
+        <v>0.16705</v>
       </c>
     </row>
     <row r="7">
@@ -4744,34 +4744,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08502999999999999</v>
+        <v>0.08581999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09293999999999999</v>
+        <v>0.09407</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1086</v>
+        <v>0.10906</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14312</v>
+        <v>0.14385</v>
       </c>
       <c r="F7" t="n">
-        <v>0.29974</v>
+        <v>0.29979</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33654</v>
+        <v>0.3373</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06494999999999999</v>
+        <v>0.05968</v>
       </c>
       <c r="I7" t="n">
-        <v>0.30284</v>
+        <v>0.30496</v>
       </c>
       <c r="J7" t="n">
-        <v>0.09776</v>
+        <v>0.08337</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1626</v>
+        <v>0.16293</v>
       </c>
     </row>
     <row r="8">
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06574000000000001</v>
+        <v>0.06254999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05013</v>
+        <v>0.04432</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02211</v>
+        <v>0.01893</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02738</v>
+        <v>0.02273</v>
       </c>
       <c r="F8" t="n">
-        <v>0.35699</v>
+        <v>0.35142</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06494999999999999</v>
+        <v>0.05968</v>
       </c>
       <c r="H8" t="n">
-        <v>0.81779</v>
+        <v>0.84605</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09634</v>
+        <v>0.07843</v>
       </c>
       <c r="J8" t="n">
-        <v>0.20916</v>
+        <v>0.27623</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.08155</v>
+        <v>-0.08683</v>
       </c>
     </row>
     <row r="9">
@@ -4818,34 +4818,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2994</v>
+        <v>0.30251</v>
       </c>
       <c r="C9" t="n">
-        <v>0.17717</v>
+        <v>0.18114</v>
       </c>
       <c r="D9" t="n">
-        <v>0.15822</v>
+        <v>0.1595</v>
       </c>
       <c r="E9" t="n">
-        <v>0.36819</v>
+        <v>0.37041</v>
       </c>
       <c r="F9" t="n">
-        <v>0.29257</v>
+        <v>0.29062</v>
       </c>
       <c r="G9" t="n">
-        <v>0.30284</v>
+        <v>0.30496</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09634</v>
+        <v>0.07843</v>
       </c>
       <c r="I9" t="n">
-        <v>4.051</v>
+        <v>4.05556</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.18107</v>
+        <v>-0.23409</v>
       </c>
       <c r="K9" t="n">
-        <v>0.16004</v>
+        <v>0.15976</v>
       </c>
     </row>
     <row r="10">
@@ -4855,34 +4855,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02781</v>
+        <v>0.02195</v>
       </c>
       <c r="C10" t="n">
-        <v>0.029</v>
+        <v>0.01569</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03853</v>
+        <v>0.02984</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.00262</v>
+        <v>-0.0148</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01411</v>
+        <v>-0.03583</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09776</v>
+        <v>0.08337</v>
       </c>
       <c r="H10" t="n">
-        <v>0.20916</v>
+        <v>0.27623</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.18107</v>
+        <v>-0.23409</v>
       </c>
       <c r="J10" t="n">
-        <v>0.31609</v>
+        <v>0.45886</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0091</v>
+        <v>-0.02728</v>
       </c>
     </row>
     <row r="11">
@@ -4892,34 +4892,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03914</v>
+        <v>0.04032</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0397</v>
+        <v>0.04094</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06123</v>
+        <v>0.06143</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05671</v>
+        <v>0.05719</v>
       </c>
       <c r="F11" t="n">
-        <v>0.16894</v>
+        <v>0.16705</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1626</v>
+        <v>0.16293</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.08155</v>
+        <v>-0.08683</v>
       </c>
       <c r="I11" t="n">
-        <v>0.16004</v>
+        <v>0.15976</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0091</v>
+        <v>-0.02728</v>
       </c>
       <c r="K11" t="n">
-        <v>0.13313</v>
+        <v>0.13218</v>
       </c>
     </row>
   </sheetData>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -5115,7 +5115,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -5195,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -5235,7 +5235,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -5315,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -5355,7 +5355,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.67797</v>
+        <v>0.69541</v>
       </c>
     </row>
   </sheetData>
@@ -5431,34 +5431,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.46036</v>
+        <v>0.47585</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01929</v>
+        <v>0.01912</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01043</v>
+        <v>0.0104</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01276</v>
+        <v>0.01274</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0431</v>
+        <v>0.04279</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03193</v>
+        <v>0.03157</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02468</v>
+        <v>0.02301</v>
       </c>
       <c r="I2" t="n">
-        <v>0.11241</v>
+        <v>0.11128</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01044</v>
+        <v>0.008070000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01469</v>
+        <v>0.01483</v>
       </c>
     </row>
     <row r="3">
@@ -5468,34 +5468,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01929</v>
+        <v>0.01912</v>
       </c>
       <c r="C3" t="n">
-        <v>0.44241</v>
+        <v>0.45862</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01701</v>
+        <v>0.01692</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01832</v>
+        <v>0.01831</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03261</v>
+        <v>0.03246</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03489</v>
+        <v>0.03461</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01882</v>
+        <v>0.01631</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06652</v>
+        <v>0.06662999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01089</v>
+        <v>0.00577</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01491</v>
+        <v>0.01506</v>
       </c>
     </row>
     <row r="4">
@@ -5505,34 +5505,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01043</v>
+        <v>0.0104</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01701</v>
+        <v>0.01692</v>
       </c>
       <c r="D4" t="n">
-        <v>0.45704</v>
+        <v>0.47262</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02795</v>
+        <v>0.02755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04032</v>
+        <v>0.03951</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04077</v>
+        <v>0.04012</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0083</v>
+        <v>0.00696</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0594</v>
+        <v>0.05868</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01447</v>
+        <v>0.01098</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02299</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="5">
@@ -5542,34 +5542,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01276</v>
+        <v>0.01274</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01832</v>
+        <v>0.01831</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02795</v>
+        <v>0.02755</v>
       </c>
       <c r="E5" t="n">
-        <v>0.49146</v>
+        <v>0.5065</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05465</v>
+        <v>0.05367</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05373</v>
+        <v>0.05292</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01028</v>
+        <v>0.008359999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.13824</v>
+        <v>0.13626</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.00098</v>
+        <v>-0.00545</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02129</v>
+        <v>0.02104</v>
       </c>
     </row>
     <row r="6">
@@ -5579,34 +5579,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0431</v>
+        <v>0.04279</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03261</v>
+        <v>0.03246</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04032</v>
+        <v>0.03951</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05465</v>
+        <v>0.05367</v>
       </c>
       <c r="F6" t="n">
-        <v>0.68834</v>
+        <v>0.6979300000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.11254</v>
+        <v>0.11029</v>
       </c>
       <c r="H6" t="n">
-        <v>0.13403</v>
+        <v>0.12928</v>
       </c>
       <c r="I6" t="n">
-        <v>0.10985</v>
+        <v>0.10691</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0053</v>
+        <v>-0.01318</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06343</v>
+        <v>0.06145</v>
       </c>
     </row>
     <row r="7">
@@ -5616,34 +5616,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03193</v>
+        <v>0.03157</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03489</v>
+        <v>0.03461</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04077</v>
+        <v>0.04012</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05373</v>
+        <v>0.05292</v>
       </c>
       <c r="F7" t="n">
-        <v>0.11254</v>
+        <v>0.11029</v>
       </c>
       <c r="G7" t="n">
-        <v>0.54978</v>
+        <v>0.56368</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02438</v>
+        <v>0.02195</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1137</v>
+        <v>0.11218</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0367</v>
+        <v>0.03067</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06105</v>
+        <v>0.05994</v>
       </c>
     </row>
     <row r="8">
@@ -5653,34 +5653,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02468</v>
+        <v>0.02301</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01882</v>
+        <v>0.01631</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0083</v>
+        <v>0.00696</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01028</v>
+        <v>0.008359999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.13403</v>
+        <v>0.12928</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02438</v>
+        <v>0.02195</v>
       </c>
       <c r="H8" t="n">
-        <v>0.73047</v>
+        <v>0.75083</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03617</v>
+        <v>0.02885</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07853</v>
+        <v>0.10162</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.03062</v>
+        <v>-0.03194</v>
       </c>
     </row>
     <row r="9">
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.11241</v>
+        <v>0.11128</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06652</v>
+        <v>0.06662999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0594</v>
+        <v>0.05868</v>
       </c>
       <c r="E9" t="n">
-        <v>0.13824</v>
+        <v>0.13626</v>
       </c>
       <c r="F9" t="n">
-        <v>0.10985</v>
+        <v>0.10691</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1137</v>
+        <v>0.11218</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03617</v>
+        <v>0.02885</v>
       </c>
       <c r="I9" t="n">
-        <v>1.94437</v>
+        <v>1.9315</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.06798</v>
+        <v>-0.08612</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06009</v>
+        <v>0.05877</v>
       </c>
     </row>
     <row r="10">
@@ -5727,34 +5727,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01044</v>
+        <v>0.008070000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01089</v>
+        <v>0.00577</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01447</v>
+        <v>0.01098</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.00098</v>
+        <v>-0.00545</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0053</v>
+        <v>-0.01318</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0367</v>
+        <v>0.03067</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07853</v>
+        <v>0.10162</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06798</v>
+        <v>-0.08612</v>
       </c>
       <c r="J10" t="n">
-        <v>0.54211</v>
+        <v>0.60839</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.00342</v>
+        <v>-0.01004</v>
       </c>
     </row>
     <row r="11">
@@ -5764,34 +5764,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01469</v>
+        <v>0.01483</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01491</v>
+        <v>0.01506</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02299</v>
+        <v>0.0226</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02129</v>
+        <v>0.02104</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06343</v>
+        <v>0.06145</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06105</v>
+        <v>0.05994</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.03062</v>
+        <v>-0.03194</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06009</v>
+        <v>0.05877</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.00342</v>
+        <v>-0.01004</v>
       </c>
       <c r="K11" t="n">
-        <v>0.47341</v>
+        <v>0.48822</v>
       </c>
     </row>
   </sheetData>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09836</v>
+        <v>0.09855</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05055</v>
+        <v>0.05173</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08951000000000001</v>
+        <v>0.08978999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -5987,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1812</v>
+        <v>0.18188</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.70558</v>
+        <v>0.70224</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -6067,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33654</v>
+        <v>0.3373</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.81779</v>
+        <v>0.84605</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.051</v>
+        <v>4.05556</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -6187,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.31609</v>
+        <v>0.45886</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.13313</v>
+        <v>0.13218</v>
       </c>
     </row>
   </sheetData>
@@ -6303,34 +6303,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09836</v>
+        <v>0.09855</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01774</v>
+        <v>0.01727</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.009390000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01173</v>
+        <v>0.0115</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03964</v>
+        <v>0.03865</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02937</v>
+        <v>0.02852</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0227</v>
+        <v>0.02078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1034</v>
+        <v>0.10051</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.00729</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01352</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="3">
@@ -6340,34 +6340,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01774</v>
+        <v>0.01727</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05055</v>
+        <v>0.05173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01565</v>
+        <v>0.01529</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01685</v>
+        <v>0.01654</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03</v>
+        <v>0.02932</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0321</v>
+        <v>0.03126</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01731</v>
+        <v>0.01473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06118</v>
+        <v>0.06019</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01001</v>
+        <v>0.00521</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01371</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="4">
@@ -6377,34 +6377,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.009390000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01565</v>
+        <v>0.01529</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08951000000000001</v>
+        <v>0.08978999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02571</v>
+        <v>0.02488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03708</v>
+        <v>0.03569</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0375</v>
+        <v>0.03624</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00764</v>
+        <v>0.00629</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05464</v>
+        <v>0.053</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01331</v>
+        <v>0.00991</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02115</v>
+        <v>0.02041</v>
       </c>
     </row>
     <row r="5">
@@ -6414,34 +6414,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01173</v>
+        <v>0.0115</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01685</v>
+        <v>0.01654</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02571</v>
+        <v>0.02488</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1812</v>
+        <v>0.18188</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05027</v>
+        <v>0.04847</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04942</v>
+        <v>0.0478</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00946</v>
+        <v>0.00755</v>
       </c>
       <c r="I5" t="n">
-        <v>0.12715</v>
+        <v>0.12307</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0009</v>
+        <v>-0.00492</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01959</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="6">
@@ -6451,34 +6451,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03964</v>
+        <v>0.03865</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03</v>
+        <v>0.02932</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03708</v>
+        <v>0.03569</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05027</v>
+        <v>0.04847</v>
       </c>
       <c r="F6" t="n">
-        <v>0.70558</v>
+        <v>0.70224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.10351</v>
+        <v>0.09961</v>
       </c>
       <c r="H6" t="n">
-        <v>0.12328</v>
+        <v>0.11677</v>
       </c>
       <c r="I6" t="n">
-        <v>0.10104</v>
+        <v>0.09656000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.00487</v>
+        <v>-0.01191</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05834</v>
+        <v>0.05551</v>
       </c>
     </row>
     <row r="7">
@@ -6488,34 +6488,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02937</v>
+        <v>0.02852</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0321</v>
+        <v>0.03126</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0375</v>
+        <v>0.03624</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04942</v>
+        <v>0.0478</v>
       </c>
       <c r="F7" t="n">
-        <v>0.10351</v>
+        <v>0.09961</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33654</v>
+        <v>0.3373</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02243</v>
+        <v>0.01983</v>
       </c>
       <c r="I7" t="n">
-        <v>0.10458</v>
+        <v>0.10133</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03376</v>
+        <v>0.0277</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05615</v>
+        <v>0.05414</v>
       </c>
     </row>
     <row r="8">
@@ -6525,34 +6525,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0227</v>
+        <v>0.02078</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01731</v>
+        <v>0.01473</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00764</v>
+        <v>0.00629</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00946</v>
+        <v>0.00755</v>
       </c>
       <c r="F8" t="n">
-        <v>0.12328</v>
+        <v>0.11677</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02243</v>
+        <v>0.01983</v>
       </c>
       <c r="H8" t="n">
-        <v>0.81779</v>
+        <v>0.84605</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03327</v>
+        <v>0.02606</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07223</v>
+        <v>0.09178</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02816</v>
+        <v>-0.02885</v>
       </c>
     </row>
     <row r="9">
@@ -6562,34 +6562,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1034</v>
+        <v>0.10051</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06118</v>
+        <v>0.06019</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05464</v>
+        <v>0.053</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12715</v>
+        <v>0.12307</v>
       </c>
       <c r="F9" t="n">
-        <v>0.10104</v>
+        <v>0.09656000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.10458</v>
+        <v>0.10133</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03327</v>
+        <v>0.02606</v>
       </c>
       <c r="I9" t="n">
-        <v>4.051</v>
+        <v>4.05556</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.06253</v>
+        <v>-0.07778</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05527</v>
+        <v>0.05308</v>
       </c>
     </row>
     <row r="10">
@@ -6599,34 +6599,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.00729</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01001</v>
+        <v>0.00521</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01331</v>
+        <v>0.00991</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0009</v>
+        <v>-0.00492</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.00487</v>
+        <v>-0.01191</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03376</v>
+        <v>0.0277</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07223</v>
+        <v>0.09178</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06253</v>
+        <v>-0.07778</v>
       </c>
       <c r="J10" t="n">
-        <v>0.31609</v>
+        <v>0.45886</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.00314</v>
+        <v>-0.00907</v>
       </c>
     </row>
     <row r="11">
@@ -6636,34 +6636,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01352</v>
+        <v>0.0134</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01371</v>
+        <v>0.0136</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02115</v>
+        <v>0.02041</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01959</v>
+        <v>0.019</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05834</v>
+        <v>0.05551</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05615</v>
+        <v>0.05414</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.02816</v>
+        <v>-0.02885</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05527</v>
+        <v>0.05308</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.00314</v>
+        <v>-0.00907</v>
       </c>
       <c r="K11" t="n">
-        <v>0.13313</v>
+        <v>0.13218</v>
       </c>
     </row>
   </sheetData>
@@ -6742,31 +6742,31 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.72845</v>
+        <v>0.72794</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2962</v>
+        <v>0.30054</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2545</v>
+        <v>0.25859</v>
       </c>
       <c r="F2" t="n">
-        <v>0.43575</v>
+        <v>0.44212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.46736</v>
+        <v>0.47073</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23178</v>
+        <v>0.21662</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4743</v>
+        <v>0.47852</v>
       </c>
       <c r="J2" t="n">
-        <v>0.15772</v>
+        <v>0.10321</v>
       </c>
       <c r="K2" t="n">
-        <v>0.34199</v>
+        <v>0.35325</v>
       </c>
     </row>
     <row r="3">
@@ -6776,34 +6776,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.72845</v>
+        <v>0.72794</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.67369</v>
+        <v>0.67499</v>
       </c>
       <c r="E3" t="n">
-        <v>0.50969</v>
+        <v>0.51308</v>
       </c>
       <c r="F3" t="n">
-        <v>0.45995</v>
+        <v>0.46299</v>
       </c>
       <c r="G3" t="n">
-        <v>0.71253</v>
+        <v>0.71216</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24652</v>
+        <v>0.21187</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3915</v>
+        <v>0.39545</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2294</v>
+        <v>0.10182</v>
       </c>
       <c r="K3" t="n">
-        <v>0.48396</v>
+        <v>0.49515</v>
       </c>
     </row>
     <row r="4">
@@ -6813,34 +6813,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2962</v>
+        <v>0.30054</v>
       </c>
       <c r="C4" t="n">
-        <v>0.67369</v>
+        <v>0.67499</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.58456</v>
+        <v>0.5860300000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.42728</v>
+        <v>0.42777</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6257200000000001</v>
+        <v>0.62669</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08172</v>
+        <v>0.06866999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.26275</v>
+        <v>0.26432</v>
       </c>
       <c r="J4" t="n">
-        <v>0.22906</v>
+        <v>0.147</v>
       </c>
       <c r="K4" t="n">
-        <v>0.56091</v>
+        <v>0.56391</v>
       </c>
     </row>
     <row r="5">
@@ -6850,34 +6850,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2545</v>
+        <v>0.25859</v>
       </c>
       <c r="C5" t="n">
-        <v>0.50969</v>
+        <v>0.51308</v>
       </c>
       <c r="D5" t="n">
-        <v>0.58456</v>
+        <v>0.5860300000000001</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.40709</v>
+        <v>0.40819</v>
       </c>
       <c r="G5" t="n">
-        <v>0.57956</v>
+        <v>0.58078</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07113</v>
+        <v>0.05794</v>
       </c>
       <c r="I5" t="n">
-        <v>0.42975</v>
+        <v>0.43128</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01095</v>
+        <v>-0.05124</v>
       </c>
       <c r="K5" t="n">
-        <v>0.36515</v>
+        <v>0.36886</v>
       </c>
     </row>
     <row r="6">
@@ -6887,34 +6887,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.43575</v>
+        <v>0.44212</v>
       </c>
       <c r="C6" t="n">
-        <v>0.45995</v>
+        <v>0.46299</v>
       </c>
       <c r="D6" t="n">
-        <v>0.42728</v>
+        <v>0.42777</v>
       </c>
       <c r="E6" t="n">
-        <v>0.40709</v>
+        <v>0.40819</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.61512</v>
+        <v>0.61599</v>
       </c>
       <c r="H6" t="n">
-        <v>0.46996</v>
+        <v>0.45592</v>
       </c>
       <c r="I6" t="n">
-        <v>0.17305</v>
+        <v>0.17221</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.02987</v>
+        <v>-0.06312</v>
       </c>
       <c r="K6" t="n">
-        <v>0.55123</v>
+        <v>0.54831</v>
       </c>
     </row>
     <row r="7">
@@ -6924,34 +6924,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.46736</v>
+        <v>0.47073</v>
       </c>
       <c r="C7" t="n">
-        <v>0.71253</v>
+        <v>0.71216</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6257200000000001</v>
+        <v>0.62669</v>
       </c>
       <c r="E7" t="n">
-        <v>0.57956</v>
+        <v>0.58078</v>
       </c>
       <c r="F7" t="n">
-        <v>0.61512</v>
+        <v>0.61599</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1238</v>
+        <v>0.11172</v>
       </c>
       <c r="I7" t="n">
-        <v>0.25937</v>
+        <v>0.26074</v>
       </c>
       <c r="J7" t="n">
-        <v>0.29974</v>
+        <v>0.21192</v>
       </c>
       <c r="K7" t="n">
-        <v>0.76819</v>
+        <v>0.77166</v>
       </c>
     </row>
     <row r="8">
@@ -6961,34 +6961,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23178</v>
+        <v>0.21662</v>
       </c>
       <c r="C8" t="n">
-        <v>0.24652</v>
+        <v>0.21187</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08172</v>
+        <v>0.06866999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07113</v>
+        <v>0.05794</v>
       </c>
       <c r="F8" t="n">
-        <v>0.46996</v>
+        <v>0.45592</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1238</v>
+        <v>0.11172</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05293</v>
+        <v>0.04234</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41138</v>
+        <v>0.44333</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.24714</v>
+        <v>-0.25966</v>
       </c>
     </row>
     <row r="9">
@@ -6998,34 +6998,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4743</v>
+        <v>0.47852</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3915</v>
+        <v>0.39545</v>
       </c>
       <c r="D9" t="n">
-        <v>0.26275</v>
+        <v>0.26432</v>
       </c>
       <c r="E9" t="n">
-        <v>0.42975</v>
+        <v>0.43128</v>
       </c>
       <c r="F9" t="n">
-        <v>0.17305</v>
+        <v>0.17221</v>
       </c>
       <c r="G9" t="n">
-        <v>0.25937</v>
+        <v>0.26074</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05293</v>
+        <v>0.04234</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.16001</v>
+        <v>-0.1716</v>
       </c>
       <c r="K9" t="n">
-        <v>0.21792</v>
+        <v>0.2182</v>
       </c>
     </row>
     <row r="10">
@@ -7035,34 +7035,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.15772</v>
+        <v>0.10321</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2294</v>
+        <v>0.10182</v>
       </c>
       <c r="D10" t="n">
-        <v>0.22906</v>
+        <v>0.147</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01095</v>
+        <v>-0.05124</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.02987</v>
+        <v>-0.06312</v>
       </c>
       <c r="G10" t="n">
-        <v>0.29974</v>
+        <v>0.21192</v>
       </c>
       <c r="H10" t="n">
-        <v>0.41138</v>
+        <v>0.44333</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.16001</v>
+        <v>-0.1716</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.04435</v>
+        <v>-0.11079</v>
       </c>
     </row>
     <row r="11">
@@ -7072,31 +7072,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.34199</v>
+        <v>0.35325</v>
       </c>
       <c r="C11" t="n">
-        <v>0.48396</v>
+        <v>0.49515</v>
       </c>
       <c r="D11" t="n">
-        <v>0.56091</v>
+        <v>0.56391</v>
       </c>
       <c r="E11" t="n">
-        <v>0.36515</v>
+        <v>0.36886</v>
       </c>
       <c r="F11" t="n">
-        <v>0.55123</v>
+        <v>0.54831</v>
       </c>
       <c r="G11" t="n">
-        <v>0.76819</v>
+        <v>0.77166</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.24714</v>
+        <v>-0.25966</v>
       </c>
       <c r="I11" t="n">
-        <v>0.21792</v>
+        <v>0.2182</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.04435</v>
+        <v>-0.11079</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
